--- a/Datacenter-Radar/MiT_Datacenter_Radar_CH_V1.0.xlsx
+++ b/Datacenter-Radar/MiT_Datacenter_Radar_CH_V1.0.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,6 +169,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1657,12 +1666,12 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Herbst 2026</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
-          <t>pruefen</t>
+          <t>Implenia (Core and Shell)</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -1703,12 +1712,12 @@
       </c>
       <c r="T6" s="12" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/stack-tops-out-swiss-data-center-completes-construction-in-melbourne/ | https://amstein-walthert.ch/de/projekte/rechenzentrum-beringen-schaffhausen/ | https://algorithmwatch.ch/de/recherche-rechenzentren-schweiz/</t>
+          <t>https://implenia.com/medien/artikel/implenia-gewinnt-attraktive-hochbau-auftraege-in-der-schweiz-und-in-deutschland/ | https://amstein-walthert.ch/de/projekte/rechenzentrum-beringen-schaffhausen/ | https://mbap.ch/de/referenzen/datacenter-zur2,-beringen/ | https://www.datacenterdynamics.com/en/news/stack-tops-out-swiss-data-center-completes-construction-in-melbourne/</t>
         </is>
       </c>
       <c r="U6" s="22" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="V6" s="15" t="inlineStr">
@@ -1718,7 +1727,7 @@
       </c>
       <c r="W6" s="12" t="inlineStr">
         <is>
-          <t>36 MW, gebaut auf dem Areal des ehemaligen SIG-Tennisclubs. Kanton musste ein neues Unterwerk bauen, finanziert vom Betreiber. Netzanschluss-Termin ist der Hebel fuer Bridging Power. Baubewilligung in rund drei Monaten erteilt. GU nicht belegt. Amstein + Walthert fuehrt das RZ Beringen als eigenes Projekt, genaue Rolle und Gewerk pruefen.</t>
+          <t>36 MW, Areal des ehemaligen SIG-Tennisclubs. GU ist Implenia, Core and Shell, achtes Datacenter von Implenia in der Schweiz seit 2020. IBN laut Implenia Herbst 2026. MBA Projektmanagement fuehrt ZUR02 als Referenz: Hauptgebaeude, Buerogebaeude, mehrere Kuehlanlagen, zwei Generatorgebaeude mit Tankraeumen, Rolle pruefen. Amstein + Walthert beteiligt, Rolle pruefen. Kanton baut neues Unterwerk, finanziert vom Betreiber, Netzanschluss-Termin ist der Hebel fuer Bridging Power.</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1814,7 @@
       </c>
       <c r="U7" s="22" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="V7" s="15" t="inlineStr">
@@ -1815,7 +1824,7 @@
       </c>
       <c r="W7" s="12" t="inlineStr">
         <is>
-          <t>Spatenstich am 26.08.2026. 15 MW IT-Leistung auf rund 6300 m2, sechs Datenhallen. Fertigstellung 2028, danach rund 60 MW Campus-Gesamtleistung. Abwaermenetz zusammen mit der Gemeinde Opfikon. Vorlaufzeit Trocknung rund fuenf Monate, das Fenster ist jetzt. GU und Fachplaner nicht belegt.</t>
+          <t>Spatenstich am 26.08.2026. 15 MW IT-Leistung auf rund 6300 m2, sechs Datenhallen. Fertigstellung 2028, danach rund 60 MW Campus-Gesamtleistung. Abwaermenetz zusammen mit der Gemeinde Opfikon. Vorlaufzeit Trocknung rund fuenf Monate, das Fenster ist jetzt. GU und Fachplaner nicht belegt. Planerkreis der Vorgaengerbauten ZUR2 und ZUR3: IKON Ingenieure und Drees &amp; Sommer, Kandidaten fuer ZUR4, nicht belegt.</t>
         </is>
       </c>
     </row>
@@ -1897,12 +1906,12 @@
       </c>
       <c r="T8" s="12" t="inlineStr">
         <is>
-          <t>https://www.presseportal.de/pm/152183/5635701 | https://www.baublatt.ch/bauprojekte/baustart-fuer-zwei-neue-datacenter-auf-metro-campus-in-dielsdorf-erfolgt-35044</t>
+          <t>https://www.presseportal.de/pm/152183/5635701 | https://mbap.ch/de/referenzen/metro-campus-zurich/ | https://www.einsarchitekten.ch/projekte/metro-campus-green | https://www.emchberger.ch/de/neubau-metro-campus-zuerich-dielsdorf-digitalisierung-zwischen-energieeffizienz-und-nachhaltigkeit?division=76</t>
         </is>
       </c>
       <c r="U8" s="22" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="V8" s="15" t="inlineStr">
@@ -1912,7 +1921,7 @@
       </c>
       <c r="W8" s="12" t="inlineStr">
         <is>
-          <t>Zwei Gebaeude, zusammen 35 MW, rund 4000 Racks auf 11600 m2. Campus 46000 m2. Implenia hat auf dem Campus bereits zwei Datacenter und ein Buerogebaeude gebaut. Abwaermenutzung durch Energie 360. IBN-Termin nicht belegt, Fachplaner nicht belegt.</t>
+          <t>Zwei Gebaeude, zusammen 35 MW, rund 4000 Racks auf 11600 m2, Campus 46000 m2. GU Implenia. Campus-Planung: MBA Projektmanagement als Generalplaner fuer drei Datacenter und drei Buerogebaeude, Eins Architekten als Architekturpartner, Emch+Berger beteiligt laut eigener Referenz, Rollen im Detail pruefen. Vollausbau laut Architekt: 27 USV-Anlagen, 24 Kaeltemaschinen, 33 MW Kaelteleistung, 15000 m2 Whitespace. Abwaermenutzung durch Energie 360. IBN-Termin und Fachplaner Elektro nicht belegt.</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2066,7 @@
       </c>
       <c r="J10" s="22" t="inlineStr">
         <is>
-          <t>pruefen</t>
+          <t>Amstein + Walthert (im Planerteam)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -2093,12 +2102,12 @@
       </c>
       <c r="T10" s="12" t="inlineStr">
         <is>
-          <t>https://www.erne-gruppe.ch/de/news/newsdetail/ernenews/medienmitteilung-flexbase/ | https://www.zhk.ch/de/wirtschaft-und-politik/news/flexbase-erhaelt-baufreigabe-fuer-technologiezentrum.html | https://www.datacenter-insider.de/flexbase-errichtet-technologiezentrum-mit-480-mw-ki-rechenzentrum-a-befea6134cb5045aba28a650a2ef6206/</t>
+          <t>https://www.erne-gruppe.ch/de/news/newsdetail/ernenews/medienmitteilung-flexbase/ | https://flexbase.ch/en/project-overview | https://www.frei-architekten.ch/projekte/technologiezentrum-flexbase-2 | https://www.datacenter-insider.de/flexbase-errichtet-technologiezentrum-mit-480-mw-ki-rechenzentrum-a-befea6134cb5045aba28a650a2ef6206/</t>
         </is>
       </c>
       <c r="U10" s="22" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="V10" s="15" t="inlineStr">
@@ -2108,7 +2117,7 @@
       </c>
       <c r="W10" s="12" t="inlineStr">
         <is>
-          <t>Baufreigabe erteilt. KI-Rechenzentrum mit bis zu 480 MW Rechenleistung auf rund 12000 m2 IT-Netzflaeche, dazu Redox-Flow-Speicher mit ueber 1.6 GWh und ueber 800 MW auf rund 20000 m2, direkt beim Unterwerk Stern von Laufenburg. 480 MW ist Rechenleistung laut Quelle, nicht als elektrische Anschlussleistung uebernehmen, deshalb Spalte F auf pruefen. Inbetriebnahme Sommer 2028.</t>
+          <t>Baufreigabe erteilt, ERNE ist GU in strategischer Partnerschaft mit FlexBase. Planerteam laut FlexBase-Projektuebersicht: Frei Architekten, Amstein + Walthert, Schnetzer Puskas (Tragwerk), Koch + Partner. Equans Schweiz und Georg Fischer planen die Integration der Megabatterie und den Netzanschluss. KI-Rechenzentrum bis 480 MW Rechenleistung auf rund 12000 m2 IT-Netzflaeche, Redox-Flow-Speicher ueber 1.6 GWh, direkt beim Unterwerk Stern von Laufenburg. 480 MW ist Rechenleistung laut Quelle, nicht als elektrische Anschlussleistung uebernehmen. IBN Sommer 2028.</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2206,7 @@
       </c>
       <c r="U11" s="22" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="V11" s="15" t="inlineStr">
@@ -2207,7 +2216,7 @@
       </c>
       <c r="W11" s="12" t="inlineStr">
         <is>
-          <t>Zaehlung eingeordnet: Der Campus umfasst die Gebaeude M (Betrieb seit Anfang 2023) sowie N und O (im Bau). Das hier gemeldete weitere Datacenter waere das vierte Gebaeude. Baublatt zaehlt es als viertes, Netzwoche als drittes mit Baustart 2026 und 5800 m2, je nachdem ob N und O einzeln gezaehlt werden. Beide URLs in T. Kapazitaet, IBN, GU und Fachplaner nicht belegt. Green investiert laut Tages-Anzeiger insgesamt rund CHF 500 Mio in den Campus.</t>
+          <t>Zaehlung eingeordnet: Der Campus umfasst die Gebaeude M (Betrieb seit Anfang 2023) sowie N und O (im Bau). Das hier gemeldete weitere Datacenter waere das vierte Gebaeude. Baublatt zaehlt es als viertes, Netzwoche als drittes mit Baustart 2026 und 5800 m2, je nachdem ob N und O einzeln gezaehlt werden. Beide URLs in T. Kapazitaet, IBN, GU und Fachplaner nicht belegt. Green investiert laut Tages-Anzeiger insgesamt rund CHF 500 Mio in den Campus. Campus-Planerteam wie N und O: MBA Projektmanagement, Eins Architekten, Emch+Berger, siehe deren Referenzseiten.</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2300,12 @@
       </c>
       <c r="T12" s="12" t="inlineStr">
         <is>
-          <t>https://www.inside-it.ch/equinix-baut-data-center-in-zuerich-aus-20241112 | https://www.netzwoche.ch/news/2024-11-13/equinix-baut-zuercher-rechenzentrum-aus</t>
+          <t>https://www.inside-it.ch/equinix-baut-data-center-in-zuerich-aus-20241112 | https://www.hrs.ch/de/projekte/equinix-rechenzentren | https://www.netzwoche.ch/news/2024-11-13/equinix-baut-zuercher-rechenzentrum-aus</t>
         </is>
       </c>
       <c r="U12" s="22" t="inlineStr">
         <is>
-          <t>13.11.2024</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="V12" s="15" t="inlineStr">
@@ -2306,7 +2315,7 @@
       </c>
       <c r="W12" s="12" t="inlineStr">
         <is>
-          <t>Sechste Ausbauphase, Investition rund CHF 40 Mio, Abschluss 2027. Rund 680 m2 zusaetzlicher Whitespace und rund 200 neue Cabinets. Ausbau im laufenden Betrieb, deshalb Betreiber-Kanal statt GU. Quelle vom November 2024, aktuelleren Stand suchen.</t>
+          <t>Sechste Ausbauphase, Investition rund CHF 40 Mio, Abschluss 2027. Rund 680 m2 zusaetzlicher Whitespace und rund 200 neue Cabinets. Ausbau im laufenden Betrieb, deshalb Betreiber-Kanal statt GU. Quelle vom November 2024, aktuelleren Stand suchen. HRS war GU der Equinix-Erweiterung ZH5.4 in Oberengstringen, Bauzeit Dezember 2020 bis Februar 2022, rund CHF 23 Mio, Architekt Itten + Brechbuehl. Kandidat auch fuer den ZH4-Ausbau, pruefen.</t>
         </is>
       </c>
     </row>
@@ -2324,21 +2333,25 @@
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>pruefen</t>
+          <t>Arlesheim</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>pruefen</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="F13" s="19" t="n">
         <v>4.5</v>
       </c>
-      <c r="G13" s="22" t="inlineStr"/>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>Bewilligung</t>
+        </is>
+      </c>
       <c r="H13" s="22" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>Mitte 2027</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -2351,7 +2364,11 @@
           <t>pruefen</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr"/>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>Fachplaner</t>
+        </is>
+      </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
           <t>Lastbank im Cx, PQ-Messung Klasse A, spaeter Wartungsfenster</t>
@@ -2359,7 +2376,7 @@
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t>Cx-Fenster vermutlich 2026 bis 2027, Termin verifizieren</t>
+          <t>Bewilligungsphase, Planer- und Baustrom-Fenster oeffnet mit der Baufreigabe</t>
         </is>
       </c>
       <c r="N13" s="22" t="inlineStr">
@@ -2380,12 +2397,12 @@
       </c>
       <c r="T13" s="12" t="inlineStr">
         <is>
-          <t>https://www.netzwoche.ch/news/2026-06-03/so-praesentiert-sich-der-schweizer-markt-fuer-rechenzentren | https://www.datacenter-insider.de/northc-plant-sechstes-schweizer-rechenzentrum-in-basel-a-d051a0a594bcb4f730589892caf8a25f/</t>
+          <t>https://www.itreseller.ch/Artikel/103958/NorthC_baut_Rechenzentrum_auf_dem_Campus_UptownBasel.html | https://netzpalaver.de/2025/09/11/northc-baut-auf-dem-campus-uptownbasel-das-rechenzentrum-der-zukunft/ | https://www.netzwoche.ch/news/2026-06-03/so-praesentiert-sich-der-schweizer-markt-fuer-rechenzentren</t>
         </is>
       </c>
       <c r="U13" s="22" t="inlineStr">
         <is>
-          <t>03.06.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="V13" s="15" t="inlineStr">
@@ -2395,7 +2412,7 @@
       </c>
       <c r="W13" s="12" t="inlineStr">
         <is>
-          <t>4.5 MW IT-Leistung, Betrieb ab 2027 gemeldet. Der Campus UptownBasel ist in den Quellen nur als Campusname belegt, Gemeinde und Kanton stehen dort nicht. Deshalb Standort und Kt. auf pruefen, Phase und Kanal leer. Beim naechsten Lauf ueber die Betreiberseite aufloesen.</t>
+          <t>Erste Etappe 2500 m2 auf dem Innovationscampus UptownBasel in Arlesheim BL, Anschluss 6 MVA, rund 5.5 MW nutzbare Leistung, davon 4.5 MW IT laut Netzwoche, kVA und kW hier sauber auseinanderhalten. Bauzeit rund 18 Monate ab Baubewilligung, Betrieb ab Mitte 2027, Notstrom mit HVO-Diesel, Abwaerme ins regionale Waermenetz. Erweitert die NorthC-Standorte Muenchenstein 1 und 2. GU und Fachplaner nicht belegt.</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2550,7 @@
       </c>
       <c r="I15" s="22" t="inlineStr">
         <is>
-          <t>pruefen</t>
+          <t>HRS (GU laut Fachpresse)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -2574,12 +2591,12 @@
       </c>
       <c r="T15" s="12" t="inlineStr">
         <is>
-          <t>https://vantage-dc.com/news/vantage-data-centers-expands-emea-portfolio-with-second-zurich-campus-fueled-by-more-than-chf-370-million-investment/ | https://www.datacenterdynamics.com/en/news/vantage-launches-second-data-center-in-switzerland/</t>
+          <t>https://vantage-dc.com/news/vantage-data-centers-expands-emea-portfolio-with-second-zurich-campus-fueled-by-more-than-chf-370-million-investment/ | https://www.immobilienbusiness.ch/en/regionen/2024-04-24/glattfelden-neuer-datencenter-campus-auf-zwei-hektaren/ | https://www.datacenterdynamics.com/en/news/vantage-launches-second-data-center-in-switzerland/</t>
         </is>
       </c>
       <c r="U15" s="22" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="V15" s="15" t="inlineStr">
@@ -2589,7 +2606,7 @@
       </c>
       <c r="W15" s="12" t="inlineStr">
         <is>
-          <t>24 MW kritische IT-Kapazitaet, rund 21000 m2, Investition ueber CHF 370 Mio, rund 30 km noerdlich von Zuerich, zusammen mit ZRH1 64 MW. Widerspruch vom Erstlauf aufgeloest: Firmenmeldung und DCD belegen die Eroeffnung im Sommer 2024. Die Meldung zu einer Eroeffnung im Sommer 2026 bezog sich auf eine weitere Ausbauetappe, Etappenplan pruefen. N+1-Redundanz, Abwaerme an Hotel und Seminarzentrum.</t>
+          <t>24 MW kritische IT-Kapazitaet, rund 21000 m2, Investition ueber CHF 370 Mio, rund 30 km noerdlich von Zuerich, zusammen mit ZRH1 64 MW. Widerspruch vom Erstlauf aufgeloest: Firmenmeldung und DCD belegen die Eroeffnung im Sommer 2024. Die Meldung zu einer Eroeffnung im Sommer 2026 bezog sich auf eine weitere Ausbauetappe, Etappenplan pruefen. N+1-Redundanz, Abwaerme an Hotel und Seminarzentrum. GU des Baus war HRS laut Immobilien Business.</t>
         </is>
       </c>
     </row>
@@ -2801,29 +2818,27 @@
           <t>ZH</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>Betrieb</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>pruefen</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
-        <is>
-          <t>Betrieb</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>pruefen</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
-        <is>
-          <t>pruefen</t>
-        </is>
-      </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>Gruner (beteiligt, Rolle pruefen)</t>
+          <t>IKON Ingenieure (alle Phasen)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -2859,12 +2874,12 @@
       </c>
       <c r="T18" s="12" t="inlineStr">
         <is>
-          <t>https://www.netzwoche.ch/news/2026-06-03/so-praesentiert-sich-der-schweizer-markt-fuer-rechenzentren | https://www.grunerfriends.com/projects/data-center-zur3-zurich | https://www.ikon.ch/referenzprojekte/neubau-rechenzentrum-digital-realty-zuerich-zur3-vormals-interxion-zur3</t>
+          <t>https://www.ikon.ch/referenzprojekte/neubau-rechenzentrum-digital-realty-zuerich-zur3-vormals-interxion-zur3 | https://www.dreso.com/ch/projekte/details/datacenter-zur3-zuerich-campus-interxion | https://www.netzwoche.ch/news/2026-06-03/so-praesentiert-sich-der-schweizer-markt-fuer-rechenzentren</t>
         </is>
       </c>
       <c r="U18" s="22" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="V18" s="15" t="inlineStr">
@@ -2874,7 +2889,7 @@
       </c>
       <c r="W18" s="12" t="inlineStr">
         <is>
-          <t>Eines der flaechenmaessig groessten Rechenzentren der Schweiz, 11400 m2 Nutzflaeche, frueher Interxion ZUR3. Liegt auf demselben Campus wie der ZUR4-Neubau. Kapazitaet in MW nicht belegt. Gruner nennt ZUR3 als Projekt im eigenen Portfolio, Rolle pruefen. Gleicher Planer-Kreis koennte beim ZUR4-Neubau wieder drin sein.</t>
+          <t>Groesstes RZ der Schweiz nach Flaeche, 11400 m2 Whitespace, 24 MW IT-Last im Endausbau laut IKON, gebaut in drei Etappen, schwieriger Baugrund mit Grundwasser bis Terrain. IKON Ingenieure planten alle Phasen bis Bauleitung, auch schon ZUR2. Drees &amp; Sommer fuehrte das Projektmanagement. Liegt auf demselben Campus wie der ZUR4-Neubau, derselbe Planerkreis ist dort der naheliegende Kandidat.</t>
         </is>
       </c>
     </row>
@@ -2954,12 +2969,12 @@
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>https://www.inside-it.ch/bald-ist-baubeginn-fuer-das-49-millionen-rechenzentrum-der-eth-zuerich-20230908</t>
+          <t>https://www.inside-it.ch/bald-ist-baubeginn-fuer-das-49-millionen-rechenzentrum-der-eth-zuerich-20230908 | https://ethz.ch/en/campus/development/construction-projects/hrz-projekt.html | https://mbap.ch/de/referenzen/hrz-eth-zuerich/</t>
         </is>
       </c>
       <c r="U19" s="22" t="inlineStr">
         <is>
-          <t>08.09.2023</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="V19" s="15" t="inlineStr">
@@ -2969,7 +2984,7 @@
       </c>
       <c r="W19" s="12" t="inlineStr">
         <is>
-          <t>Fuenfgeschossig, ueber 4000 m2, Baukosten rund CHF 49 Mio. Spatenstich April 2024, Bauarbeiten bis Ende 2025 geplant, IT-Betrieb ab Anfang 2026. Quelle von 2023, aktueller Stand nicht belegt, deshalb Phase leer. Oeffentlicher Bauherr, Beschaffung laeuft ueber simap.ch.</t>
+          <t>Fuenfgeschossig, ueber 4000 m2, Baukosten rund CHF 49 Mio, Spatenstich April 2024, IT-Betrieb ab Anfang 2026 geplant. Generalplaner-Team ueber offenes GATT/WTO-Verfahren, Architektur Penzel Valier. MBA Projektmanagement fuehrt HRZ als eigene Referenz, Rolle pruefen. Oeffentlicher Bauherr, Beschaffung ueber simap.ch, aktueller Baustand verifizieren.</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11604,7 +11619,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>ZUR02 Beringen (STACK Infrastructure)</t>
+          <t>ZUR02 Beringen (STACK) | Technologiezentrum Laufenburg (FlexBase)</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
@@ -11634,7 +11649,7 @@
       </c>
       <c r="M53" s="12" t="inlineStr">
         <is>
-          <t>Fuehrt das RZ Beringen als eigenes Projekt, Rolle pruefen. Weitere DC-Referenzen: Raiffeisen St. Gallen (USV-Ersatz), ETH LEE, Accarda Bruettisellen. Quelle: amstein-walthert.ch/de/projekte/rechenzentrum-beringen-schaffhausen/</t>
+          <t>Fuehrt das RZ Beringen als eigenes Projekt, Rolle pruefen. Weitere DC-Referenzen: Raiffeisen St. Gallen (USV-Ersatz), ETH LEE, Accarda Bruettisellen. Quelle: amstein-walthert.ch/de/projekte/rechenzentrum-beringen-schaffhausen/ Zusaetzlich im Planerteam des FlexBase TZL Laufenburg belegt, flexbase.ch/en/project-overview. Zwei Radar-Projekte.</t>
         </is>
       </c>
     </row>
@@ -11806,6 +11821,918 @@
       <c r="M56" s="12" t="inlineStr">
         <is>
           <t>Fuehrt ein Datacenter-Projekt Suisse romande als Referenz, Projekt und Rolle pruefen. Kandidat fuer den Romandie-Kanal, NorthC The Hive. Quelle: afry.com/fr-ch/projet/datacenter-suisse-romande</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>Implenia AG</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>GU/TU Datacenter (Bereich Buildings)</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D57" s="25" t="inlineStr">
+        <is>
+          <t>GU/TU</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>Lupfig DC4, Dielsdorf N+O, ZUR02 Beringen (alle im Radar)</t>
+        </is>
+      </c>
+      <c r="F57" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G57" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H57" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I57" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J57" s="27" t="n"/>
+      <c r="K57" s="27" t="n"/>
+      <c r="L57" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="12" t="inlineStr">
+        <is>
+          <t>Drei laufende Radar-Projekte gleichzeitig, achtes Schweizer DC seit 2020. Der wichtigste GU-Kontakt im Radar. Quelle: implenia.com Medienmitteilungen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>HRS Real Estate AG</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>GU/TU Datacenter</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D58" s="25" t="inlineStr">
+        <is>
+          <t>GU/TU</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>ZRH2 Glattfelden (Vantage), Equinix ZH5.4 Oberengstringen</t>
+        </is>
+      </c>
+      <c r="F58" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G58" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H58" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I58" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J58" s="27" t="n"/>
+      <c r="K58" s="27" t="n"/>
+      <c r="L58" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="12" t="inlineStr">
+        <is>
+          <t>GU fuer Vantage ZRH2 und die Equinix-Erweiterung ZH5.4 (CHF 23 Mio, 2020 bis 2022). Quelle: hrs.ch/de/projekte/equinix-rechenzentren, immobilienbusiness.ch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>MBA Projektmanagement AG</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>Generalplanung, Projektmanagement DC</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D59" s="25" t="inlineStr">
+        <is>
+          <t>Fachplaner</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>Green Metro-Campus Dielsdorf, ZUR02 Beringen, ETH HRZ, SCS ZH-Herdern</t>
+        </is>
+      </c>
+      <c r="F59" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G59" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H59" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I59" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J59" s="27" t="n"/>
+      <c r="K59" s="27" t="n"/>
+      <c r="L59" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="12" t="inlineStr">
+        <is>
+          <t>Vier belegte DC-Referenzen, davon drei im Radar. Meistvernetzter Planer-Kontakt. Quelle: mbap.ch/de/referenzen/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="25" t="inlineStr">
+        <is>
+          <t>IKON Ingenieure AG</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>Planung und Bauleitung DC</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="inlineStr">
+        <is>
+          <t>Fachplaner</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>ZUR2 und ZUR3 Glattbrugg (Digital Realty), Kandidat ZUR4</t>
+        </is>
+      </c>
+      <c r="F60" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G60" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H60" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I60" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J60" s="27" t="n"/>
+      <c r="K60" s="27" t="n"/>
+      <c r="L60" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="12" t="inlineStr">
+        <is>
+          <t>Alle Phasen bei zwei Glattbrugg-Neubauten. Direktester Zugang zum ZUR4-Cx. Quelle: ikon.ch Referenzprojekte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="25" t="inlineStr">
+        <is>
+          <t>Drees &amp; Sommer Schweiz AG</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>Projektmanagement DC</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D61" s="25" t="inlineStr">
+        <is>
+          <t>Fachplaner</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>ZUR3 Glattbrugg (Digital Realty)</t>
+        </is>
+      </c>
+      <c r="F61" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G61" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H61" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I61" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J61" s="27" t="n"/>
+      <c r="K61" s="27" t="n"/>
+      <c r="L61" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="12" t="inlineStr">
+        <is>
+          <t>Projektmanagement ZUR3 Campus. Quelle: dreso.com/ch/projekte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="25" t="inlineStr">
+        <is>
+          <t>Eins Architekten AG</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Architektur DC</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D62" s="25" t="inlineStr">
+        <is>
+          <t>Fachplaner</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>Green Metro-Campus Dielsdorf</t>
+        </is>
+      </c>
+      <c r="F62" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G62" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H62" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I62" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J62" s="27" t="n"/>
+      <c r="K62" s="27" t="n"/>
+      <c r="L62" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="12" t="inlineStr">
+        <is>
+          <t>Architekturpartner von MBA fuer drei Datacenter und drei Buerogebaeude. Quelle: einsarchitekten.ch/projekte/metro-campus-green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
+          <t>Emch+Berger AG</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>Ingenieurleistungen DC</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D63" s="25" t="inlineStr">
+        <is>
+          <t>Fachplaner</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>Green Metro-Campus Dielsdorf</t>
+        </is>
+      </c>
+      <c r="F63" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G63" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H63" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I63" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J63" s="27" t="n"/>
+      <c r="K63" s="27" t="n"/>
+      <c r="L63" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="12" t="inlineStr">
+        <is>
+          <t>Beteiligt laut eigener Referenzseite, Rolle pruefen. Quelle: emchberger.ch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="25" t="inlineStr">
+        <is>
+          <t>ERNE AG Bauunternehmung</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>GU Technologiezentrum</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D64" s="25" t="inlineStr">
+        <is>
+          <t>GU/TU</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>Technologiezentrum Laufenburg (FlexBase)</t>
+        </is>
+      </c>
+      <c r="F64" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G64" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H64" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I64" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J64" s="27" t="n"/>
+      <c r="K64" s="27" t="n"/>
+      <c r="L64" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="12" t="inlineStr">
+        <is>
+          <t>Strategische Partnerschaft mit FlexBase, Tiefbau laeuft. Quelle: erne-gruppe.ch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>Frei Architekten AG</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Architektur</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D65" s="25" t="inlineStr">
+        <is>
+          <t>Fachplaner</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>Technologiezentrum Laufenburg (FlexBase)</t>
+        </is>
+      </c>
+      <c r="F65" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G65" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H65" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I65" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J65" s="27" t="n"/>
+      <c r="K65" s="27" t="n"/>
+      <c r="L65" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="12" t="inlineStr">
+        <is>
+          <t>Im Planerteam laut FlexBase-Projektuebersicht. Quelle: frei-architekten.ch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="25" t="inlineStr">
+        <is>
+          <t>Schnetzer Puskas Ingenieure</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>Tragwerksplanung</t>
+        </is>
+      </c>
+      <c r="C66" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
+          <t>Fachplaner</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>Technologiezentrum Laufenburg (FlexBase)</t>
+        </is>
+      </c>
+      <c r="F66" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G66" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H66" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I66" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J66" s="27" t="n"/>
+      <c r="K66" s="27" t="n"/>
+      <c r="L66" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="12" t="inlineStr">
+        <is>
+          <t>Im Planerteam laut FlexBase-Projektuebersicht. Quelle: flexbase.ch/en/project-overview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>Koch + Partner</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>Rolle pruefen</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D67" s="25" t="inlineStr">
+        <is>
+          <t>Fachplaner</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>Technologiezentrum Laufenburg (FlexBase)</t>
+        </is>
+      </c>
+      <c r="F67" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G67" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H67" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I67" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J67" s="27" t="n"/>
+      <c r="K67" s="27" t="n"/>
+      <c r="L67" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="12" t="inlineStr">
+        <is>
+          <t>Im Planerteam genannt, Disziplin nicht belegt. Quelle: flexbase.ch/en/project-overview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="25" t="inlineStr">
+        <is>
+          <t>Equans Schweiz AG</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>Technik, Batterie-Integration</t>
+        </is>
+      </c>
+      <c r="C68" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D68" s="25" t="inlineStr">
+        <is>
+          <t>Elektro-Installateur</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>Technologiezentrum Laufenburg (FlexBase)</t>
+        </is>
+      </c>
+      <c r="F68" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G68" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H68" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I68" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J68" s="27" t="n"/>
+      <c r="K68" s="27" t="n"/>
+      <c r="L68" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="12" t="inlineStr">
+        <is>
+          <t>Plant mit Georg Fischer die Integration der Megabatterie und den Netzanschluss. Quelle: flexbase.ch/en/project-overview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="25" t="inlineStr">
+        <is>
+          <t>Georg Fischer AG</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>Industriepartner Batterie</t>
+        </is>
+      </c>
+      <c r="C69" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D69" s="25" t="inlineStr">
+        <is>
+          <t>Fachplaner</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>Technologiezentrum Laufenburg (FlexBase)</t>
+        </is>
+      </c>
+      <c r="F69" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G69" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H69" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I69" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J69" s="27" t="n"/>
+      <c r="K69" s="27" t="n"/>
+      <c r="L69" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="12" t="inlineStr">
+        <is>
+          <t>Mit Equans fuer Batterie-Integration und Netzanschluss genannt. Quelle: flexbase.ch/en/project-overview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="25" t="inlineStr">
+        <is>
+          <t>Itten + Brechbuehl AG</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>Architektur</t>
+        </is>
+      </c>
+      <c r="C70" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D70" s="25" t="inlineStr">
+        <is>
+          <t>Fachplaner</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>Equinix ZH5.4 Oberengstringen</t>
+        </is>
+      </c>
+      <c r="F70" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G70" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H70" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I70" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J70" s="27" t="n"/>
+      <c r="K70" s="27" t="n"/>
+      <c r="L70" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="12" t="inlineStr">
+        <is>
+          <t>Architekt der Equinix-Erweiterung ZH5.4 unter GU HRS. Quelle: hrs.ch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="25" t="inlineStr">
+        <is>
+          <t>Penzel Valier AG</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>Architektur, Generalplanung</t>
+        </is>
+      </c>
+      <c r="C71" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D71" s="25" t="inlineStr">
+        <is>
+          <t>Fachplaner</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>Rechenzentrum Hoenggerberg (ETH Zuerich)</t>
+        </is>
+      </c>
+      <c r="F71" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G71" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H71" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I71" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J71" s="27" t="n"/>
+      <c r="K71" s="27" t="n"/>
+      <c r="L71" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="12" t="inlineStr">
+        <is>
+          <t>Architektur im Generalplaner-Team des HRZ. Quelle: ethz.ch Bauprojekte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="25" t="inlineStr">
+        <is>
+          <t>DPR Construction</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>GU Gebaeude 1 ZRH1</t>
+        </is>
+      </c>
+      <c r="C72" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="D72" s="25" t="inlineStr">
+        <is>
+          <t>GU/TU</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>ZRH1 Winterthur (Vantage)</t>
+        </is>
+      </c>
+      <c r="F72" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="G72" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="H72" s="26" t="inlineStr">
+        <is>
+          <t>FEHLT</t>
+        </is>
+      </c>
+      <c r="I72" s="25" t="inlineStr">
+        <is>
+          <t>Kalt</t>
+        </is>
+      </c>
+      <c r="J72" s="27" t="n"/>
+      <c r="K72" s="27" t="n"/>
+      <c r="L72" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="12" t="inlineStr">
+        <is>
+          <t>Baute Gebaeude 1 (ZRH11) auf dem Vantage-Campus Winterthur. Quelle: dpr.com/projects.</t>
         </is>
       </c>
     </row>
@@ -12999,7 +13926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13668,6 +14595,285 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="B25" s="18">
+        <f>WEEKNUM(DATE(2026,8,30),21)</f>
+        <v/>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>ZUR02 Beringen (STACK)</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>GU belegt: Implenia baut ZUR02 als Core and Shell, IBN Herbst 2026 laut Implenia. MBA Projektmanagement fuehrt das Projekt ebenfalls als Referenz, inklusive Generatorgebaeude und Kuehlanlagen.</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>https://implenia.com/medien/artikel/implenia-gewinnt-attraktive-hochbau-auftraege-in-der-schweiz-und-in-deutschland/</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Implenia haelt damit drei Radar-Projekte gleichzeitig: Lupfig, Dielsdorf und Beringen. Ein Implenia-Kontakt auf Bereichsebene Datacenter oeffnet alle drei Baustellen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="B26" s="18">
+        <f>WEEKNUM(DATE(2026,8,30),21)</f>
+        <v/>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Technologiezentrum Laufenburg (FlexBase)</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Planerteam belegt: Frei Architekten, Amstein + Walthert, Schnetzer Puskas, Koch + Partner. Equans und Georg Fischer fuer Batterie-Integration und Netzanschluss.</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>https://flexbase.ch/en/project-overview</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Amstein + Walthert sitzt jetzt belegt an zwei Radar-Projekten, Beringen und Laufenburg. Das A+W-Gespraech deckt beide ab und ist damit der wertvollste Planertermin im Radar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="B27" s="18">
+        <f>WEEKNUM(DATE(2026,8,30),21)</f>
+        <v/>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Metro-Campus Dielsdorf N und O (Green)</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Campus-Planerteam belegt: MBA Projektmanagement als Generalplaner, Eins Architekten, Emch+Berger. Vollausbau 27 USV, 24 Kaeltemaschinen, 33 MW Kaelte, 15000 m2 Whitespace.</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>https://mbap.ch/de/referenzen/metro-campus-zurich/</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>33 MW Kaelteleistung heisst grosse Heat-Load-Tests im Cx. MBA plant den ganzen Campus, ein Termin dort deckt N, O und das kommende vierte Gebaeude ab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="B28" s="18">
+        <f>WEEKNUM(DATE(2026,8,30),21)</f>
+        <v/>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>ZRH2 Glattfelden (Vantage)</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>GU nachgetragen: HRS hat den Campus gebaut, Quelle Immobilien Business.</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>https://www.immobilienbusiness.ch/en/regionen/2024-04-24/glattfelden-neuer-datencenter-campus-auf-zwei-hektaren/</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>HRS baut fuer Vantage und fuer Equinix. Zweiter GU-Multiplikator neben Implenia, Kontakt auf HRS-Bereichsebene Datacenter suchen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="B29" s="18">
+        <f>WEEKNUM(DATE(2026,8,30),21)</f>
+        <v/>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>ZH4 Zuerich (Equinix)</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>HRS als bisheriger Equinix-GU belegt: Erweiterung ZH5.4 Oberengstringen, CHF 23 Mio, Architekt Itten + Brechbuehl. GU des laufenden ZH4-Ausbaus weiter offen.</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hrs.ch/de/projekte/equinix-rechenzentren</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Wer den ZH4-Ausbau baut, vergibt auch die temporaere Versorgung waehrend der Umschaltungen. HRS zuerst fragen, die kennen beide Betreiber.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="B30" s="18">
+        <f>WEEKNUM(DATE(2026,8,30),21)</f>
+        <v/>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>ZUR3 Glattbrugg (Digital Realty)</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Planer belegt: IKON Ingenieure alle Phasen (auch ZUR2), Drees &amp; Sommer Projektmanagement. Kapazitaet belegt: 24 MW IT im Endausbau laut IKON.</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ikon.ch/referenzprojekte/neubau-rechenzentrum-digital-realty-zuerich-zur3-vormals-interxion-zur3</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>IKON kennt den Campus Glattbrugg aus zwei Neubauten. Fuer den ZUR4-Cx ist IKON der direkteste Planer-Zugang, vor dem LV ansprechen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="B31" s="18">
+        <f>WEEKNUM(DATE(2026,8,30),21)</f>
+        <v/>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>UptownBasel Campus (NorthC)</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Standort und Termin belegt: Arlesheim BL, erste Etappe 2500 m2, 6 MVA Anschluss, rund 5.5 MW nutzbar, Bauzeit 18 Monate ab Bewilligung, Betrieb Mitte 2027. Phase auf Bewilligung gesetzt.</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>https://netzpalaver.de/2025/09/11/northc-baut-auf-dem-campus-uptownbasel-das-rechenzentrum-der-zukunft/</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Betrieb Mitte 2027 heisst Cx Anfang 2027, das Fenster fuer den Planer-Einstieg ist jetzt. HVO-Notstrom passt exakt zum MiT-Portfolio, Stage V und HVO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="B32" s="18">
+        <f>WEEKNUM(DATE(2026,8,30),21)</f>
+        <v/>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Rechenzentrum Hoenggerberg (ETH)</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Planerseite belegt: Generalplaner-Team aus offenem Verfahren, Architektur Penzel Valier, MBA Projektmanagement mit HRZ-Referenz.</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>https://ethz.ch/en/campus/development/construction-projects/hrz-projekt.html</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>MBA taucht damit beim dritten Radar-Projekt auf, Dielsdorf, Beringen und ETH. MBA ist der still meistvernetzte Player im Schweizer DC-Bau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="B33" s="18">
+        <f>WEEKNUM(DATE(2026,8,30),21)</f>
+        <v/>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>03_Kontakte, Partner-Netz</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>16 Partnerfirmen mit belegten Projektzuordnungen ergaenzt: Implenia, HRS, MBA, IKON, Drees &amp; Sommer, Eins Architekten, Emch+Berger, ERNE, Frei Architekten, Schnetzer Puskas, Koch + Partner, Equans, Georg Fischer, Itten + Brechbuehl, Penzel Valier, DPR Construction. Personen und Kontaktdaten als FEHLT.</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>https://mbap.ch/de/referenzen/</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Das Partner-Netz steht. Drei Multiplikatoren stechen heraus: Implenia (drei Projekte), MBA (drei Projekte), HRS (zwei Betreiber). Diese drei zuerst.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
